--- a/members_data.xlsx
+++ b/members_data.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Name</t>
   </si>
@@ -34,12 +34,6 @@
   </si>
   <si>
     <t>922956646</t>
-  </si>
-  <si>
-    <t>Barsiisaa Margaa</t>
-  </si>
-  <si>
-    <t>930308503</t>
   </si>
   <si>
     <t>Dajanee Guutaa</t>
@@ -441,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -506,10 +500,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -517,10 +511,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
         <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
       </c>
       <c r="C7">
         <v>10000</v>
@@ -530,8 +524,8 @@
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
-        <v>16</v>
+      <c r="B8">
+        <v>912861288</v>
       </c>
       <c r="C8">
         <v>10000</v>
@@ -539,10 +533,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9">
-        <v>912861288</v>
+        <v>923151421</v>
       </c>
       <c r="C9">
         <v>10000</v>
@@ -550,23 +544,12 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10">
-        <v>923151421</v>
+        <v>912356447</v>
       </c>
       <c r="C10">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11">
-        <v>912356447</v>
-      </c>
-      <c r="C11">
         <v>10000</v>
       </c>
     </row>

--- a/members_data.xlsx
+++ b/members_data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Name</t>
   </si>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>Walfaanaa Magarsaa</t>
-  </si>
-  <si>
-    <t>Jabeessaa Dhugumaa</t>
   </si>
   <si>
     <t>Naggasaa Dheeressaa</t>
@@ -435,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -536,20 +533,9 @@
         <v>16</v>
       </c>
       <c r="B9">
-        <v>923151421</v>
+        <v>912356447</v>
       </c>
       <c r="C9">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10">
-        <v>912356447</v>
-      </c>
-      <c r="C10">
         <v>10000</v>
       </c>
     </row>

--- a/members_data.xlsx
+++ b/members_data.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walfaanaam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Waltana\Desktop\EGSA_Lottery_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="10044"/>
+    <workbookView xWindow="132" yWindow="576" windowWidth="22716" windowHeight="9996"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Name</t>
   </si>
@@ -36,12 +36,6 @@
     <t>922956646</t>
   </si>
   <si>
-    <t>Dajanee Guutaa</t>
-  </si>
-  <si>
-    <t>913216895</t>
-  </si>
-  <si>
     <t>Lalisee Magarsaa</t>
   </si>
   <si>
@@ -67,6 +61,9 @@
   </si>
   <si>
     <t>Walfaanaa Magarsaa</t>
+  </si>
+  <si>
+    <t>Total money for winners</t>
   </si>
   <si>
     <t>Naggasaa Dheeressaa</t>
@@ -98,7 +95,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -121,13 +118,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -432,15 +443,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,8 +462,11 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -461,8 +476,11 @@
       <c r="C2">
         <v>10000</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -472,8 +490,11 @@
       <c r="C3">
         <v>10000</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -483,60 +504,64 @@
       <c r="C4">
         <v>10000</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
       <c r="C5">
         <v>10000</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
       <c r="C6">
         <v>10000</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
-        <v>14</v>
+      <c r="B7">
+        <v>912861288</v>
       </c>
       <c r="C7">
         <v>10000</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <v>130000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8">
-        <v>912861288</v>
+        <v>912356447</v>
       </c>
       <c r="C8">
         <v>10000</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9">
-        <v>912356447</v>
-      </c>
-      <c r="C9">
-        <v>10000</v>
+      <c r="D8">
+        <v>80000</v>
       </c>
     </row>
   </sheetData>

--- a/members_data.xlsx
+++ b/members_data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Name</t>
   </si>
@@ -67,6 +67,9 @@
   </si>
   <si>
     <t>Naggasaa Dheeressaa</t>
+  </si>
+  <si>
+    <t>Oromiyaa Walfaanaa</t>
   </si>
 </sst>
 </file>
@@ -443,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
@@ -491,7 +494,7 @@
         <v>10000</v>
       </c>
       <c r="D3">
-        <v>130000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -519,7 +522,7 @@
         <v>10000</v>
       </c>
       <c r="D5">
-        <v>130000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -547,7 +550,7 @@
         <v>10000</v>
       </c>
       <c r="D7">
-        <v>130000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -562,6 +565,20 @@
       </c>
       <c r="D8">
         <v>80000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>939173232</v>
+      </c>
+      <c r="C9">
+        <v>10000</v>
+      </c>
+      <c r="D9">
+        <v>130000</v>
       </c>
     </row>
   </sheetData>
